--- a/TDXapp/tdxAppData/tdxSZIndexs.xlsx
+++ b/TDXapp/tdxAppData/tdxSZIndexs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/TDXapp/tdxAppData/tdxSZIndexs.xlsx
+++ b/TDXapp/tdxAppData/tdxSZIndexs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/TDXapp/tdxAppData/tdxSZIndexs.xlsx
+++ b/TDXapp/tdxAppData/tdxSZIndexs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E371"/>
+  <dimension ref="A1:F371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>MarketCode</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -481,6 +486,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -508,6 +518,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -535,6 +550,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -562,6 +582,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -589,6 +614,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -616,6 +646,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -643,6 +678,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -670,6 +710,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -697,6 +742,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -724,6 +774,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -751,6 +806,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -778,6 +838,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -805,6 +870,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -832,6 +902,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -859,6 +934,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -886,6 +966,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -913,6 +998,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -940,6 +1030,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -967,6 +1062,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -994,6 +1094,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1021,6 +1126,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1048,6 +1158,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1075,6 +1190,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1102,6 +1222,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1129,6 +1254,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1156,6 +1286,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1183,6 +1318,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1210,6 +1350,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1237,6 +1382,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1264,6 +1414,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1291,6 +1446,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1318,6 +1478,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1345,6 +1510,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1372,6 +1542,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1399,6 +1574,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1426,6 +1606,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1453,6 +1638,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1480,6 +1670,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1507,6 +1702,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -1534,6 +1734,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -1561,6 +1766,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1588,6 +1798,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1615,6 +1830,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -1642,6 +1862,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1669,6 +1894,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -1696,6 +1926,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1723,6 +1958,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -1750,6 +1990,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -1777,6 +2022,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -1804,6 +2054,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -1831,6 +2086,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -1858,6 +2118,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -1885,6 +2150,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1912,6 +2182,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -1939,6 +2214,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -1966,6 +2246,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -1993,6 +2278,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -2020,6 +2310,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -2047,6 +2342,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -2074,6 +2374,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -2101,6 +2406,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -2128,6 +2438,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -2155,6 +2470,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -2182,6 +2502,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -2209,6 +2534,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -2236,6 +2566,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -2263,6 +2598,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -2290,6 +2630,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -2317,6 +2662,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -2344,6 +2694,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -2371,6 +2726,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -2398,6 +2758,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -2425,6 +2790,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -2452,6 +2822,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -2479,6 +2854,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -2506,6 +2886,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -2533,6 +2918,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -2560,6 +2950,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -2587,6 +2982,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -2614,6 +3014,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -2641,6 +3046,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -2668,6 +3078,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -2695,6 +3110,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -2722,6 +3142,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -2749,6 +3174,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -2776,6 +3206,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -2803,6 +3238,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -2830,6 +3270,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -2857,6 +3302,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -2884,6 +3334,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -2911,6 +3366,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -2938,6 +3398,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -2965,6 +3430,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -2992,6 +3462,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -3019,6 +3494,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -3046,6 +3526,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -3073,6 +3558,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -3100,6 +3590,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -3127,6 +3622,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -3154,6 +3654,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -3181,6 +3686,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -3208,6 +3718,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -3235,6 +3750,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -3262,6 +3782,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -3289,6 +3814,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -3316,6 +3846,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -3343,6 +3878,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -3370,6 +3910,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -3397,6 +3942,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -3424,6 +3974,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -3451,6 +4006,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -3478,6 +4038,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -3505,6 +4070,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -3532,6 +4102,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -3559,6 +4134,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -3586,6 +4166,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -3613,6 +4198,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -3640,6 +4230,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -3667,6 +4262,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -3694,6 +4294,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -3721,6 +4326,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -3748,6 +4358,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -3775,6 +4390,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -3802,6 +4422,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -3829,6 +4454,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -3856,6 +4486,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -3883,6 +4518,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -3910,6 +4550,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -3937,6 +4582,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -3964,6 +4614,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -3991,6 +4646,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -4018,6 +4678,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -4045,6 +4710,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -4072,6 +4742,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
@@ -4099,6 +4774,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
@@ -4126,6 +4806,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -4153,6 +4838,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -4180,6 +4870,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -4207,6 +4902,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
@@ -4234,6 +4934,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
@@ -4261,6 +4966,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
@@ -4288,6 +4998,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
@@ -4315,6 +5030,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
@@ -4342,6 +5062,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
@@ -4369,6 +5094,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
@@ -4396,6 +5126,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -4423,6 +5158,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
@@ -4450,6 +5190,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -4477,6 +5222,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -4504,6 +5254,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
@@ -4531,6 +5286,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
@@ -4558,6 +5318,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
@@ -4585,6 +5350,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
@@ -4612,6 +5382,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -4639,6 +5414,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
@@ -4666,6 +5446,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
@@ -4693,6 +5478,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
@@ -4720,6 +5510,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
@@ -4747,6 +5542,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
@@ -4774,6 +5574,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
@@ -4801,6 +5606,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
@@ -4828,6 +5638,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
@@ -4855,6 +5670,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -4882,6 +5702,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
@@ -4909,6 +5734,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
@@ -4936,6 +5766,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -4963,6 +5798,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -4990,6 +5830,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
@@ -5017,6 +5862,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
@@ -5044,6 +5894,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
@@ -5071,6 +5926,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -5098,6 +5958,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -5125,6 +5990,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
@@ -5152,6 +6022,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -5179,6 +6054,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
@@ -5206,6 +6086,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
@@ -5233,6 +6118,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
@@ -5260,6 +6150,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -5287,6 +6182,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
@@ -5314,6 +6214,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
@@ -5341,6 +6246,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
@@ -5368,6 +6278,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
@@ -5395,6 +6310,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
@@ -5422,6 +6342,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
@@ -5449,6 +6374,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
@@ -5476,6 +6406,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
@@ -5503,6 +6438,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
@@ -5530,6 +6470,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
@@ -5557,6 +6502,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
@@ -5584,6 +6534,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -5611,6 +6566,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
@@ -5638,6 +6598,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -5665,6 +6630,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -5692,6 +6662,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -5719,6 +6694,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
@@ -5746,6 +6726,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
@@ -5773,6 +6758,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -5800,6 +6790,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -5827,6 +6822,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -5854,6 +6854,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
@@ -5881,6 +6886,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -5908,6 +6918,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
@@ -5935,6 +6950,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
@@ -5962,6 +6982,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
@@ -5989,6 +7014,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
@@ -6016,6 +7046,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
@@ -6043,6 +7078,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
@@ -6070,6 +7110,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
@@ -6097,6 +7142,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
@@ -6124,6 +7174,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
@@ -6151,6 +7206,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
@@ -6178,6 +7238,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
@@ -6205,6 +7270,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
@@ -6232,6 +7302,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
@@ -6259,6 +7334,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -6286,6 +7366,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
@@ -6313,6 +7398,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
@@ -6340,6 +7430,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
@@ -6367,6 +7462,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
@@ -6394,6 +7494,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
@@ -6421,6 +7526,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
@@ -6448,6 +7558,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
@@ -6475,6 +7590,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
@@ -6502,6 +7622,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
@@ -6529,6 +7654,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
@@ -6556,6 +7686,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
@@ -6583,6 +7718,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
@@ -6610,6 +7750,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
@@ -6637,6 +7782,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
@@ -6664,6 +7814,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
@@ -6691,6 +7846,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
@@ -6718,6 +7878,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
@@ -6745,6 +7910,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
@@ -6772,6 +7942,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
@@ -6799,6 +7974,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
@@ -6826,6 +8006,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
@@ -6853,6 +8038,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
@@ -6880,6 +8070,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
@@ -6907,6 +8102,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
@@ -6934,6 +8134,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
@@ -6961,6 +8166,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
@@ -6988,6 +8198,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
@@ -7015,6 +8230,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
@@ -7042,6 +8262,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
@@ -7069,6 +8294,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
@@ -7096,6 +8326,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
@@ -7123,6 +8358,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
@@ -7150,6 +8390,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
@@ -7177,6 +8422,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
@@ -7204,6 +8454,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
@@ -7231,6 +8486,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
@@ -7258,6 +8518,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
@@ -7285,6 +8550,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
@@ -7312,6 +8582,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
@@ -7339,6 +8614,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
@@ -7366,6 +8646,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
@@ -7393,6 +8678,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
@@ -7420,6 +8710,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
@@ -7447,6 +8742,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
@@ -7474,6 +8774,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
@@ -7501,6 +8806,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
@@ -7528,6 +8838,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
@@ -7555,6 +8870,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
@@ -7582,6 +8902,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
@@ -7609,6 +8934,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
@@ -7636,6 +8966,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
@@ -7663,6 +8998,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
@@ -7690,6 +9030,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
@@ -7717,6 +9062,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
@@ -7744,6 +9094,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
@@ -7771,6 +9126,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
@@ -7798,6 +9158,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
@@ -7825,6 +9190,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
@@ -7852,6 +9222,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
@@ -7879,6 +9254,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
@@ -7906,6 +9286,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
@@ -7933,6 +9318,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
@@ -7960,6 +9350,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
@@ -7987,6 +9382,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
@@ -8014,6 +9414,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
@@ -8041,6 +9446,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
@@ -8068,6 +9478,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
@@ -8095,6 +9510,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
@@ -8122,6 +9542,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
@@ -8149,6 +9574,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
@@ -8176,6 +9606,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
@@ -8203,6 +9638,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
@@ -8230,6 +9670,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
@@ -8257,6 +9702,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
@@ -8284,6 +9734,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
@@ -8311,6 +9766,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
@@ -8338,6 +9798,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
@@ -8365,6 +9830,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
@@ -8392,6 +9862,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
@@ -8419,6 +9894,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
@@ -8446,6 +9926,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
@@ -8473,6 +9958,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
@@ -8500,6 +9990,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
@@ -8527,6 +10022,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
@@ -8554,6 +10054,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
@@ -8581,6 +10086,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
@@ -8608,6 +10118,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
@@ -8635,6 +10150,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
@@ -8662,6 +10182,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
@@ -8689,6 +10214,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
@@ -8716,6 +10246,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
@@ -8743,6 +10278,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
@@ -8770,6 +10310,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
@@ -8797,6 +10342,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
@@ -8824,6 +10374,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
@@ -8851,6 +10406,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
@@ -8878,6 +10438,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
@@ -8905,6 +10470,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
@@ -8932,6 +10502,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
@@ -8959,6 +10534,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
@@ -8986,6 +10566,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
@@ -9013,6 +10598,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
@@ -9040,6 +10630,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
@@ -9067,6 +10662,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
@@ -9094,6 +10694,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
@@ -9121,6 +10726,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
@@ -9148,6 +10758,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
@@ -9175,6 +10790,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
@@ -9202,6 +10822,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
@@ -9229,6 +10854,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
@@ -9256,6 +10886,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
@@ -9283,6 +10918,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
@@ -9310,6 +10950,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
@@ -9337,6 +10982,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
@@ -9364,6 +11014,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
@@ -9391,6 +11046,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
@@ -9418,6 +11078,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
@@ -9445,6 +11110,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
@@ -9472,6 +11142,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
@@ -9499,6 +11174,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
@@ -9526,6 +11206,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
@@ -9553,6 +11238,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
@@ -9580,6 +11270,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
@@ -9607,6 +11302,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
@@ -9634,6 +11334,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
@@ -9661,6 +11366,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
@@ -9688,6 +11398,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
@@ -9715,6 +11430,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
@@ -9742,6 +11462,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
@@ -9769,6 +11494,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
@@ -9796,6 +11526,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
@@ -9823,6 +11558,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
@@ -9850,6 +11590,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
@@ -9877,6 +11622,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
@@ -9904,6 +11654,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
@@ -9931,6 +11686,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
@@ -9958,6 +11718,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
@@ -9985,6 +11750,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
@@ -10012,6 +11782,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
@@ -10039,6 +11814,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
@@ -10066,6 +11846,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
@@ -10093,6 +11878,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
@@ -10120,6 +11910,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
@@ -10147,6 +11942,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
@@ -10174,6 +11974,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
@@ -10201,6 +12006,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
@@ -10228,6 +12038,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
@@ -10255,6 +12070,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
@@ -10282,6 +12102,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
@@ -10309,6 +12134,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
@@ -10336,6 +12166,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
@@ -10363,6 +12198,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
@@ -10390,6 +12230,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
@@ -10417,6 +12262,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>TDX</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
@@ -10442,6 +12292,11 @@
       <c r="E371" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>TDX</t>
         </is>
       </c>
     </row>
